--- a/backend_fastapi/backend_fastapi/media/excel/19_Other.xlsx
+++ b/backend_fastapi/backend_fastapi/media/excel/19_Other.xlsx
@@ -428,34 +428,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -678,70 +678,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1154 Box 8683
-DPO AE 34629</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>902-72-8574</t>
+          <t>23AADCU2395N1ZY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Abhikaran Jalonha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>05025 Mary Fall
-Mackside, OR 70036</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Smith-Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>934-70-6847</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>22083742</v>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>INV-146</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>720</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>3348.16</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>674.48</v>
+      </c>
       <c r="U2" t="n">
-        <v>7920</v>
+        <v>3877</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -752,7 +746,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>10% → 720.0</t>
+          <t>6.0% → 74.31 | 6.0% → 74.31 | 9.0% → 189.86 | 9.0% → 189.86</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -761,16 +755,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>IBAN:GB62IACN00896958403438</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>YILONG 4'x6' All over
-Handmade Carpet Dining Room
-Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
+          <t>Cetaphil DAM Advance Ultra-Hydrati-
+ng Lotion Face - 100 gm x1.0 @ 395.08 = 466.2 | Ahaglow Advanced Skin Rejuvenating
+Face Wash Gel x1.0 @ 556.34 = 656.48 | Acutret 20 mg - 10 capsules x6.0 @ 206.43 = 1387.2 | Faireye under eye cream x1.0 @ 695.8 = 821.04 | Biluma cream - 15 gm x1.0 @ 462.37 = 545.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -784,7 +774,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0.948</v>
+        <v>0.946</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -797,73 +787,71 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (3348.16) ≠ Total (3877.0). Diff: 528.84; Items sum (3876.52) ≈ Subtotal (3348.16). Diff: 528.36 (15.8%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cox LLC</t>
+          <t>Divya Suhane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>89299747</v>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>INV-147</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>353.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>3746.82</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>652.3099999999999</v>
+      </c>
       <c r="U3" t="n">
-        <v>389</v>
+        <v>4015</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -874,7 +862,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10% → 35.36</t>
+          <t>2.5% → 12.23 | 2.5% → 12.23 | 9.0% → 122.11 | 9.0% → 122.11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -883,23 +871,10 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
+          <t>Solasafe sunscreen gel spf 50 x1.0 @ 450.64 = 531.75 | Trapic 500 TA - 10 x3.0 @ 163.09 = 513.74 | Depiwhite Advanced Cream - 15 ml x1.0 @ 495.93 = 585.2 | Fixderma Shadow SPF 50+ Cream x1.0 @ 410.17 = 484.0 | Sortet F 16 mg - 10 cap x6.0 @ 316.8 = 1900.8</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -913,7 +888,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0.946</v>
+        <v>0.95</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -926,62 +901,82 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (3746.82) ≠ Total (4015.0). Diff: 268.18; Items sum (4015.49) ≈ Subtotal (3746.82). Diff: 268.67 (7.2%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>UnCue Dermacare Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TP:47107678</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5201XXXXX6713</t>
-        </is>
-      </c>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>harshit rathore</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>INV-148</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>5.917</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1076.4</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>168.24</v>
+      </c>
       <c r="U4" t="n">
-        <v>35.5</v>
+        <v>1234</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20.00% → 5.9167</t>
+          <t>6.0% → 36.39 | 6.0% → 36.39 | 9.0% → 42.28 | 9.0% → 42.28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -993,8 +988,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>(5)8410663018663
-SANDWICH CREME CHOCO = 35.5 | SURGELE @ 35.5 | ESPECES = 36.0</t>
+          <t>Zincovit tablet x6.0 @ 78.31 = 554.4 | Sevenseas Cap x2.0 @ 303.29 = 679.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1004,11 +998,11 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0.576</v>
+        <v>0.951</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1021,73 +1015,71 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Recommended field missing: Customer name (customer_name); Recommended field missing: Due date (due_date); Recommended field missing: Invoice ID (invoice_id)</t>
+          <t>Subtotal (1076.4) ≠ Total (1234.0). Diff: 157.60; Items sum (1233.76) ≈ Subtotal (1076.4). Diff: 157.36 (14.6%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>59888 Dawn Valley Suite 242
-New Marilyn, WA 49740</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wilson PLC</t>
+          <t>Karishma Bande</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>674 Leon Cape Suite 819
-Burtonstad, NE 12662</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Wilson PLC</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>963-73-0110</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>94689364</v>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>INV-149</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2015-01-12</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>33776.06</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3377.61</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>370.64</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>59.64</v>
+      </c>
       <c r="U5" t="n">
-        <v>37153.67</v>
+        <v>437</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -1098,7 +1090,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10% → 3377.61</t>
+          <t>9.0% → 33.36 | 9.0% → 33.36</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1107,26 +1099,10 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>IBAN:GB67GYBL21403855924419</t>
-        </is>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Yilong 5'x8' Handknotted Silk
-Area Rug Home Decor Kid
-Friendly Carpet L39B x4.0 @ 8000.0 = 35200.0 | Faux Fur Animal Print Hide Skin
-Rug Cowhide Area Rug Floor
-Mat Carpet 33.5"X43" x4.0 @ 26.03 = 114.53 | Garden Flower Carpet Quilted
-Bedroom Floor Princess Tapis
-Lace Rug Carpets x5.0 @ 45.5 = 250.25 | Double Dorje Carpet Tibetan
-Rug Handwoven by Artisans in
-Nepal x3.0 @ 297.0 = 980.1 | Egg Bathroom Rug Carpet Area
-Rugs Rug Floor Mats Nordic Chic
-Room Decor x2.0 @ 68.1 = 149.82 | Striped Contemporary Gabbeh
-Kashkoli Oriental Area Rug
-Handmade Wool Carpet 6x8 x1.0 @ 417.24 = 458.96</t>
+          <t>Excela Moisturiser - 50 gm x1.0 @ 370.64 = 437.36</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1140,7 +1116,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1153,53 +1129,45 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Items sum (37153.66) ≈ Subtotal (33776.06). Diff: 3377.60 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (370.64) ≠ Total (437.0). Diff: 66.36; Items sum (437.36) ≈ Subtotal (370.64). Diff: 66.72 (18.0%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cox LLC</t>
+          <t>Bhusan Naresh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>89299747</t>
+          <t>INV-150</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1207,21 +1175,25 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>353.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
+        <v>394.51</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>63.48</v>
+      </c>
       <c r="U6" t="n">
-        <v>389</v>
+        <v>466</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1232,7 +1204,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10% → 35.36</t>
+          <t>9.0% → 35.51 | 9.0% → 35.51</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1241,23 +1213,11 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
-        </is>
-      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
+          <t>Ahaglow Advanced Skin Rejuvenating
+Face Wash Gel - 100 gm x1.0 @ 394.51 = 465.52</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1271,7 +1231,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0.946</v>
+        <v>0.949</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1284,7 +1244,1036 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (394.51) ≠ Total (466.0). Diff: 71.49; Items sum (465.52) ≈ Subtotal (394.51). Diff: 71.01 (18.0%); Recommended field missing: Tax amount (tax_amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reyes, Holloway and Lee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>38676 Johnson Burg Suite 666
+West Rebeccamouth, SD 02588</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Reyes, Holloway and Lee</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Castillo LLC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>70391 Kelsey Terrace
+Garcialand, VT 41740</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Castillo LLC</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>901-88-0463</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16273983</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>744.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>819.0599999999999</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>10% → 74.46</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>IBAN:GB96VWUL52026848004193</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Handmade Thick round warm
+crochet Rug Carpet Mat 97%
+acrylic 3% me Floor Decor x4.0 @ 44.99 = 197.96 | Rug White Moroccan Beni
+Ourain Trellis Shag Area Rug
+Authentic Handmade Carpet x2.0 @ 245.0 = 539.0 | Abstract Living Room Carpet
+Home Decor Nordic Style
+Bedside Area Rug Floor Mats x1.0 @ 24.01 = 26.41 | Leopard Printed Rug Skin Mat
+Leather Faux Fur Animals Area
+Rugs Home Carpets x1.0 @ 19.49 = 21.44 | 1pc Exquisite Durable Foot
+Cloth Christmas Carpet Xmas
+Cushion for Kitchen x2.0 @ 15.57 = 34.25</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Items sum (819.06) ≈ Subtotal (744.6). Diff: 74.46 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Obrien Group</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6217 Boyd Ville Apt. 758
+Robbinsberg, AZ 54997</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Obrien Group</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Duncan-Davis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PSC 2324, Box 6632
+APO AP 93827</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Duncan-Davis</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>917-86-7656</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>72128555</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2013-12-25</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>665.76</v>
+      </c>
+      <c r="S8" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>732.34</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>10% → 66.58</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>IBAN:GB71QMAA96406297569205</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Fatawa Islamiyah (Islamic
+Verdicts) (8 Volume Set) x2.0 @ 99.9 = 219.78 | Sasinowski M-Legacy Of Ra
+BOOK NEW x1.0 @ 19.4 = 21.34 | Time Life Books: The Old West
+Series ~ Complete 26 Volumes
++ Master Index mn853 x3.0 @ 139.95 = 461.83 | Tumbling by Caela Carter x3.0 @ 4.49 = 14.82 | How to Win Friends &amp; Influence
+People x2.0 @ 6.62 = 14.56</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Items sum (732.33) ≈ Subtotal (665.76). Diff: 66.57 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Armstrong Inc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9547 Samuel Cliffs
+Samuelchester, CO 34580</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Armstrong Inc</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yu, Williams and Barry</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>34887 Craig Trail Apt. 161
+Lake Sally, CA 02955</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yu, Williams and Barry</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>940-88-3989</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>49360354</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2017-05-03</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>358.35</v>
+      </c>
+      <c r="S9" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>10% → None</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>IBAN:GB74SATA49913307165446</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Lotto Youth Boys Fuerzapura
+L500 Jr Soccer Cleats Size 2.5
+White Blue M6147 2.5Y x3.0 @ 19.99 = 65.97 | Skechers Kids' Snap Sprints
+Sneaker Size 4 Blue/Black
+975461 x5.0 @ 29.99 = 164.94 | Joma Boys Youth Super Copa
+102 Soccer Cleats 5.5 White
+Yellow Blue Futbol NEW x5.0 @ 19.99 = 109.94 | Joma Youth Boys Gol 205 Piso
+Multitaco Soccer Cleats 1.5
+White Blue Yellow NEW x2.0 @ 19.99 = 43.98 | 100Pcs Wall Stickers Home
+Decor Glow In The Dark Star
+sticker Decal Kids room x5.0 @ 1.7 = 9.35</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Items sum (394.18) ≈ Subtotal (358.35). Diff: 35.83 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kelley-Thomas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19996 Diane Well
+Port Jennifer, TX 60910</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kelley-Thomas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Green, Kelly and Matthews</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5110 Heather Ways
+Andersontown, RI 96931</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Green, Kelly and Matthews</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>61479635</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2018-07-02</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>10% → 3.0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>IBAN:GB29ZNFB26250974035092</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Executive style x5.0 @ 5.99 = 32.95</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Items sum (32.95) ≈ Subtotal (29.95). Diff: 3.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Short-Dixon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>697 Carla Parks Apt. 401
+Turnerfort, WA 66552</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Short-Dixon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>911-72-8704</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Smith, Hebert and Smith</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7860 Tiffany Drive
+North Andrewview, CT 50988</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Smith, Hebert and Smith</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>930-87-8283</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>38173030</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2018-12-17</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>5643.98</v>
+      </c>
+      <c r="S11" t="n">
+        <v>564.4</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>6208.38</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>10% → 564.4</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>IBAN:GB44UVRX06742416736608</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Yilong 5'x7.5' Hand Knotted Silk
+Area Rug Medium Size Classic
+Floor Carpets 0186 x2.0 @ 2800.0 = 6160.0 | 3pcs Faux Fur Seat Pads 30cm
+Round Cushions Fleece Floor
+Carpets Decorative x3.0 @ 14.66 = 48.38</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Items sum (6208.38) ≈ Subtotal (5643.98). Diff: 564.40 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rodriguez, White and Hernandez</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>275 Sanders Fall Suite 646
+Jenniferburgh, IA 31174</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rodriguez, White and Hernandez</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Young Inc</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0386 Kane Alley
+Zacharystad, MT 55786</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Young Inc</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>986-87-8099</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>92395596</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2011-10-03</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>10% → 0.2</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>IBAN:GB36EZLG32867912781587</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>LuLaRoe Nicole Dress Size
+Medium 11 x1.0 @ 1.99 = 2.19</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Items sum (2.19) ≈ Subtotal (1.99). Diff: 0.20 (10.1%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Parker, Khan and Parker</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2487 Todd Green Suite 559
+Jacktown, UT 04354</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Parker, Khan and Parker</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Thompson, Terry and Johnson</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>47851 Michael Rapids Suite 469
+Scottbury, MS 96580</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Thompson, Terry and Johnson</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>922-70-7690</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>35312696</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2017-05-11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>292.68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>10% → 29.27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>IBAN:GB24PPHX39330226937268</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Liza Byrd Dress Sz L- Coral
+Green Medallion Print Short
+Sleeve 100% Cotton Line x2.0 @ 17.99 = 39.58 | Bcbgeneration Black Sleeveless
+Lace Back Cut Out Dress Sz 2 x1.0 @ 2.99 = 3.29 | Tommy Bahama Women's V
+Neck Linen Floral Dress Size M
+Beige Short Sleeve Tan x2.0 @ 34.99 = 76.98 | Lands End Womens 3/4 Sleeve
+Dress Plus 3X Navy Blue Floral
+Cotton Knit 482038 x5.0 @ 21.23 = 116.77 | Fashion Sexy Backless
+Tight-fitting Halter Dress
+Cocktail Party Weeding Elegant x2.0 @ 8.8 = 19.36 | Lumiere Large Multicolored
+Orange Short Dress NWT x2.0 @ 4.99 = 10.98 | SCOTT McCINTOCK SIZE 12
+BLACK PARTY DRESS WITH
+SPARKLIND TOP x2.0 @ 25.0 = 55.0</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Items sum (321.96) ≈ Subtotal (292.68). Diff: 29.28 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thomas Group</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13710 Henry Cliff
+Jonesshire, NV 05926</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thomas Group</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>904-83-3752</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ferguson and Sons</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>082 Medina Lock Suite 628
+Alvarezport, MS 21031</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ferguson and Sons</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>942-75-5647</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>66789639</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2011-09-19</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>271.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>10% → 27.13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>IBAN:GB18TVDL00942136316502</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>KING JAMES VERSION (KJV),
+RAINBOW STUDY BIBLE, BLACK
+LEATHER with INDEX x3.0 @ 52.99 = 174.87 | The Complete Illustrated Works
+of Lewis Carroll by Carroll, Lewis
+Hardback Book x4.0 @ 10.49 = 46.16 | Sing My Way Home: Voices of
+the New American Roots x5.0 @ 5.61 = 30.86 | Obama An Intimate Portrait by
+Pete Souza P-F EBOOK / x3.0 @ 4.99 = 16.47 | Haida: Their Art and Culture x1.0 @ 4.89 = 5.38 | Summer Places x4.0 @ 4.49 = 19.76 | Michelangelo and the Popes
+Ceiling by Ross King x1.0 @ 4.49 = 4.94</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Items sum (298.44) ≈ Subtotal (271.29). Diff: 27.15 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
@@ -1299,10 +2288,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -1351,23 +2340,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>37153.67</v>
+        <v>10029</v>
       </c>
       <c r="D2" t="n">
-        <v>37153.67</v>
+        <v>2005.8</v>
       </c>
       <c r="E2" t="n">
-        <v>37153.67</v>
+        <v>437</v>
       </c>
       <c r="F2" t="n">
-        <v>37153.67</v>
+        <v>4015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1378,23 +2367,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Short-Dixon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>15840</v>
+        <v>6208.38</v>
       </c>
       <c r="D3" t="n">
-        <v>7920</v>
+        <v>6208.38</v>
       </c>
       <c r="E3" t="n">
-        <v>7920</v>
+        <v>6208.38</v>
       </c>
       <c r="F3" t="n">
-        <v>7920</v>
+        <v>6208.38</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1405,23 +2394,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>Reyes, Holloway and Lee</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>778</v>
+        <v>819.0599999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>389</v>
+        <v>819.0599999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>389</v>
+        <v>819.0599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>389</v>
+        <v>819.0599999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1432,27 +2421,162 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MARJANE OUARZAZATE</t>
+          <t>Obrien Group</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>35.5</v>
+        <v>732.34</v>
       </c>
       <c r="D5" t="n">
-        <v>35.5</v>
+        <v>732.34</v>
       </c>
       <c r="E5" t="n">
-        <v>35.5</v>
+        <v>732.34</v>
       </c>
       <c r="F5" t="n">
-        <v>35.5</v>
+        <v>732.34</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Armstrong Inc</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Parker, Khan and Parker</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="F7" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thomas Group</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="F8" t="n">
+        <v>298.42</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kelley-Thomas</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rodriguez, White and Hernandez</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>USD</t>
         </is>
       </c>
     </row>
